--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260629.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.51%</t>
+          <t>10.90%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.79%</t>
+          <t>9.76%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.52%</t>
+          <t>8.46%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.59%</t>
+          <t>7.75%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.28%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>110,567</t>
+          <t>52,193</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>4.11%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>52,193</t>
+          <t>110,567</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.47%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -968,73 +968,73 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>52,983</t>
+          <t>39,180</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>39,180</t>
+          <t>52,983</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>54,552</t>
+          <t>5,242</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1056,73 +1056,73 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>5,242</t>
+          <t>54,552</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>82,027</t>
+          <t>53,328</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>53,328</t>
+          <t>82,027</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1188,51 +1188,51 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>29,368</t>
+          <t>22,061</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>22,061</t>
+          <t>29,368</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1305,44 +1305,44 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>79,975</t>
+          <t>101,269</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>101,269</t>
+          <t>79,975</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1408,90 +1408,90 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6,261</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>14,300</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>27,464</t>
+          <t>14,300</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>46,322</t>
+          <t>27,464</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,39 +1503,39 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>6,261</t>
+          <t>7,273</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>7,273</t>
+          <t>46,322</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>149,881,605</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
